--- a/2022/North3/North3_members_final.xlsx
+++ b/2022/North3/North3_members_final.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
